--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564259.4235735289</v>
+        <v>564259</v>
       </c>
       <c r="R2" t="n">
-        <v>6452385.179715378</v>
+        <v>6452385</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564258.3358713615</v>
+        <v>564258</v>
       </c>
       <c r="R3" t="n">
-        <v>6452484.766727836</v>
+        <v>6452485</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103672</v>
+        <v>103680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105461</v>
+        <v>105470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103680</v>
+        <v>103682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105470</v>
+        <v>105473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103682</v>
+        <v>103709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105473</v>
+        <v>105501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103709</v>
+        <v>103715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105501</v>
+        <v>105507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103715</v>
+        <v>103722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105507</v>
+        <v>105514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103722</v>
+        <v>103726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105514</v>
+        <v>105518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103726</v>
+        <v>103733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105518</v>
+        <v>105525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103736</v>
+        <v>103741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105528</v>
+        <v>105533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103741</v>
+        <v>103749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105533</v>
+        <v>105541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74116478</v>
       </c>
       <c r="B2" t="n">
-        <v>103749</v>
+        <v>103759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74512127</v>
       </c>
       <c r="B3" t="n">
-        <v>105541</v>
+        <v>105551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74116478</v>
+        <v>74512127</v>
       </c>
       <c r="B2" t="n">
-        <v>103759</v>
+        <v>106060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222395</v>
+        <v>221101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Halsebo Hemgöls SV-hörn 250 m SV, Sm</t>
+          <t>Hemgölens SV-hörn 150 m SV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564259</v>
+        <v>564258</v>
       </c>
       <c r="R2" t="n">
-        <v>6452385</v>
+        <v>6452485</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 8G0d 3819. SOM: Circaea alpina. LEG: Erik Moberger</t>
+          <t>Smålands flora 2007: KOO: 8G0d 3919. SOM: Impatiens noli-tangere. LEG: Erik Moberger</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Dråg</t>
+          <t>Lucka i barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74512127</v>
+        <v>74116478</v>
       </c>
       <c r="B3" t="n">
-        <v>105551</v>
+        <v>104252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221101</v>
+        <v>222395</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemgölens SV-hörn 150 m SV, Sm</t>
+          <t>Halsebo Hemgöls SV-hörn 250 m SV, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564258</v>
+        <v>564259</v>
       </c>
       <c r="R3" t="n">
-        <v>6452485</v>
+        <v>6452385</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 8G0d 3919. SOM: Impatiens noli-tangere. LEG: Erik Moberger</t>
+          <t>Smålands flora 2007: KOO: 8G0d 3819. SOM: Circaea alpina. LEG: Erik Moberger</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lucka i barrskog</t>
+          <t>Dråg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 11501-2022 artfynd.xlsx
+++ b/artfynd/A 11501-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74512127</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74116478</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>